--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-170</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 893.880,47</t>
-  </si>
-  <si>
-    <t>R$ 4.938,57
-R$ 5.072,73</t>
-  </si>
-  <si>
-    <t>(14.0%)
-(11.7%)</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>(14.7%)</t>
-  </si>
-  <si>
-    <t>36.3%</t>
-  </si>
-  <si>
-    <t>(17.3%)</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 910.281,93</t>
+  </si>
+  <si>
+    <t>R$ 4.893,99
+R$ 5.021,52</t>
+  </si>
+  <si>
+    <t>(13.8%)
+(11.5%)</t>
+  </si>
+  <si>
+    <t>51.5</t>
+  </si>
+  <si>
+    <t>(14.5%)</t>
+  </si>
+  <si>
+    <t>26.2%</t>
+  </si>
+  <si>
+    <t>(27.1%)</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -947,13 +947,13 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>26.4</t>
-  </si>
-  <si>
-    <t>76.3%</t>
-  </si>
-  <si>
-    <t>8.4%</t>
+    <t>26.5</t>
+  </si>
+  <si>
+    <t>76.2%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
   </si>
   <si>
     <t>5.5</t>
@@ -965,13 +965,13 @@
     <t>11.8</t>
   </si>
   <si>
-    <t>18.3</t>
-  </si>
-  <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>-R$ 29.763,48</t>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>74.3%</t>
+  </si>
+  <si>
+    <t>-R$ 29.866,68</t>
   </si>
   <si>
     <t>2.94</t>
@@ -3025,7 +3025,9 @@
       <c r="AB13" s="8">
         <v>8.5071428571428562</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>17.465616000000001</v>
+      </c>
       <c r="AD13" s="8">
         <v>23.383050847457625</v>
       </c>
@@ -5841,10 +5843,10 @@
         <v>0.30769230769230771</v>
       </c>
       <c r="T35" s="6">
-        <v>30.40593247356761</v>
+        <v>3.1570995214851374</v>
       </c>
       <c r="U35" s="6">
-        <v>27.939008237420225</v>
+        <v>0.69017528533775219</v>
       </c>
       <c r="V35" s="6">
         <v>0.12004854194059691</v>
@@ -5922,7 +5924,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5958,25 +5960,59 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
+      <c r="O36" s="5">
+        <v>4367.1099999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>4367.1099999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-0.18318339100346026</v>
+      </c>
+      <c r="R36" s="7">
+        <v>43</v>
+      </c>
+      <c r="S36" s="6">
+        <v>-0.022727272727272707</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.35171264291487964</v>
+      </c>
+      <c r="U36" s="6">
+        <v>-0.014861590388151432</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.079900895557931909</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.035711488833576437</v>
+      </c>
+      <c r="X36" s="8">
+        <v>32.401332000000004</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>6.7746204545454551</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>12.218054166666667</v>
+      </c>
       <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="AD36" s="8">
+        <v>25.765331999999997</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.76000000000000001</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -6668,7 +6704,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6704,25 +6740,61 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
-      <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="O42" s="5">
+        <v>4331.0799999999999</v>
+      </c>
+      <c r="P42" s="5">
+        <v>4331.0799999999999</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.095316854569089005</v>
+      </c>
+      <c r="R42" s="7">
+        <v>51</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.04081632653061229</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.36895628803901104</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.054702106633911174</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.062883276226714815</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.013138178006409488</v>
+      </c>
+      <c r="X42" s="8">
+        <v>27.370312500000001</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.875</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.125</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>6.2634744680851071</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>7.1338531249999999</v>
+      </c>
+      <c r="AC42" s="8">
+        <v>14.321353999999999</v>
+      </c>
+      <c r="AD42" s="8">
+        <v>21.276562500000001</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.6875</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -7803,7 +7875,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7839,25 +7911,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>980.60000000000002</v>
+      </c>
+      <c r="P51" s="5">
+        <v>980.60000000000002</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.033891625615763532</v>
+      </c>
+      <c r="R51" s="7">
+        <v>9</v>
+      </c>
+      <c r="S51" s="6">
+        <v>0</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.38977156842749333</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.044290230471140113</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.086252294513563116</v>
+      </c>
+      <c r="X51" s="8">
+        <v>21.523339999999997</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>3.9799999999999995</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>8.8133400000000002</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>18.953340000000001</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8730,7 +8836,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>13.281333</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -10984,7 +11092,9 @@
       <c r="AB76" s="8">
         <v>4.1080645161290317</v>
       </c>
-      <c r="AC76" s="8"/>
+      <c r="AC76" s="8">
+        <v>7.4840439999999999</v>
+      </c>
       <c r="AD76" s="8">
         <v>16.033333333333335</v>
       </c>
@@ -14180,7 +14290,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14216,25 +14326,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>2280.3099999999999</v>
+      </c>
+      <c r="P102" s="5">
+        <v>2280.3099999999999</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.18763448521553261</v>
+      </c>
+      <c r="R102" s="7">
+        <v>23</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.2068965517241379</v>
+      </c>
+      <c r="T102" s="6">
+        <v>7.0429020615618045E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.37025641250531727</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.027957382987400838</v>
+      </c>
+      <c r="W102" s="6">
+        <v>-0.0057266336594585824</v>
+      </c>
+      <c r="X102" s="8">
+        <v>35.034261111111114</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>6.6388875000000001</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>8.9813705882352934</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>15.739705000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>21.79815</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.44444444444444442</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>-81.400000000000006</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -17056,7 +17202,7 @@
         <v>0.053072060889164732</v>
       </c>
       <c r="W125" s="6">
-        <v>0.019078332734459216</v>
+        <v>0.020690392970306733</v>
       </c>
       <c r="X125" s="8">
         <v>30.934847727272725</v>
@@ -21449,7 +21595,7 @@
         <v>0.045730943993971283</v>
       </c>
       <c r="W160" s="6">
-        <v>0.0085671152668671275</v>
+        <v>0.0077540325679283494</v>
       </c>
       <c r="X160" s="8">
         <v>29.423214285714288</v>
@@ -24776,7 +24922,9 @@
       <c r="AB186" s="8">
         <v>4.5750000000000002</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>9.46875</v>
+      </c>
       <c r="AD186" s="8">
         <v>16.422912499999999</v>
       </c>
@@ -25875,7 +26023,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>44</v>
@@ -25911,25 +26059,59 @@
       <c t="s" r="N195" s="4">
         <v>52</v>
       </c>
-      <c r="O195" s="5"/>
-      <c r="P195" s="5"/>
-      <c r="Q195" s="6"/>
-      <c r="R195" s="7"/>
-      <c r="S195" s="6"/>
-      <c r="T195" s="6"/>
-      <c r="U195" s="6"/>
-      <c r="V195" s="6"/>
-      <c r="W195" s="6"/>
-      <c r="X195" s="8"/>
-      <c r="Y195" s="6"/>
-      <c r="Z195" s="6"/>
-      <c r="AA195" s="8"/>
-      <c r="AB195" s="8"/>
+      <c r="O195" s="5">
+        <v>4442.3599999999997</v>
+      </c>
+      <c r="P195" s="5">
+        <v>4442.3599999999997</v>
+      </c>
+      <c r="Q195" s="6">
+        <v>0.15075121749041531</v>
+      </c>
+      <c r="R195" s="7">
+        <v>51</v>
+      </c>
+      <c r="S195" s="6">
+        <v>-0.019230769230769273</v>
+      </c>
+      <c r="T195" s="6">
+        <v>0.34577647916873017</v>
+      </c>
+      <c r="U195" s="6">
+        <v>-0.0080422117973329502</v>
+      </c>
+      <c r="V195" s="6">
+        <v>0.015449896001224575</v>
+      </c>
+      <c r="W195" s="6">
+        <v>-0.010844686157808012</v>
+      </c>
+      <c r="X195" s="8">
+        <v>28.757290625</v>
+      </c>
+      <c r="Y195" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="Z195" s="6">
+        <v>0.03125</v>
+      </c>
+      <c r="AA195" s="8">
+        <v>6.3996369565217393</v>
+      </c>
+      <c r="AB195" s="8">
+        <v>8.0656250000000007</v>
+      </c>
       <c r="AC195" s="8"/>
-      <c r="AD195" s="8"/>
-      <c r="AE195" s="6"/>
+      <c r="AD195" s="8">
+        <v>22.025521874999999</v>
+      </c>
+      <c r="AE195" s="6">
+        <v>0.625</v>
+      </c>
       <c r="AF195" s="9"/>
-      <c r="AG195" s="5"/>
+      <c r="AG195" s="5">
+        <v>-21.800000000000001</v>
+      </c>
       <c r="AH195" s="10">
         <v>2</v>
       </c>
@@ -27401,7 +27583,9 @@
       <c r="AB207" s="8">
         <v>7.8037000000000001</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>16.012962000000002</v>
+      </c>
       <c r="AD207" s="8">
         <v>22.955555555555556</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
@@ -912,33 +912,33 @@
   </si>
   <si>
     <t>214
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 910.281,93</t>
-  </si>
-  <si>
-    <t>R$ 4.893,99
-R$ 5.021,52</t>
+177</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 921.506,09</t>
+  </si>
+  <si>
+    <t>R$ 4.901,63
+R$ 5.028,19</t>
   </si>
   <si>
     <t>(13.8%)
 (11.5%)</t>
   </si>
   <si>
-    <t>51.5</t>
+    <t>51.6</t>
   </si>
   <si>
     <t>(14.5%)</t>
   </si>
   <si>
-    <t>26.2%</t>
-  </si>
-  <si>
-    <t>(27.1%)</t>
+    <t>26.3%</t>
+  </si>
+  <si>
+    <t>(26.8%)</t>
   </si>
   <si>
     <t>3.6%</t>
@@ -947,10 +947,10 @@
     <t>0.6%</t>
   </si>
   <si>
-    <t>26.5</t>
-  </si>
-  <si>
-    <t>76.2%</t>
+    <t>26.4</t>
+  </si>
+  <si>
+    <t>76.4%</t>
   </si>
   <si>
     <t>8.5%</t>
@@ -968,7 +968,7 @@
     <t>18.4</t>
   </si>
   <si>
-    <t>74.3%</t>
+    <t>74.4%</t>
   </si>
   <si>
     <t>-R$ 29.866,68</t>
@@ -2066,7 +2066,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2102,25 +2102,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>8444.5599999999995</v>
+      </c>
+      <c r="P6" s="5">
+        <v>8444.5599999999995</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.044021454883838906</v>
+      </c>
+      <c r="R6" s="7">
+        <v>79</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.10227272727272729</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.34910994770597881</v>
+      </c>
+      <c r="U6" s="6">
+        <v>-0.01178392953570109</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.045198802542702053</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.015274212037098441</v>
+      </c>
+      <c r="X6" s="8">
+        <v>21.032121818181817</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>5.5162443037974684</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.4966055555555555</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>6.7250880000000004</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>13.620605454545453</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.96363636363636362</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>0</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -6002,7 +6038,9 @@
       <c r="AB36" s="8">
         <v>12.218054166666667</v>
       </c>
-      <c r="AC36" s="8"/>
+      <c r="AC36" s="8">
+        <v>19.578721000000002</v>
+      </c>
       <c r="AD36" s="8">
         <v>25.765331999999997</v>
       </c>
@@ -7953,7 +7991,9 @@
       <c r="AB51" s="8">
         <v>8.8133400000000002</v>
       </c>
-      <c r="AC51" s="8"/>
+      <c r="AC51" s="8">
+        <v>12.196666</v>
+      </c>
       <c r="AD51" s="8">
         <v>18.953340000000001</v>
       </c>
@@ -20126,10 +20166,10 @@
         <v>-0.36956521739130432</v>
       </c>
       <c r="T148" s="6">
-        <v>0</v>
+        <v>0.070142291184623395</v>
       </c>
       <c r="U148" s="6">
-        <v>-0.35611152446722938</v>
+        <v>-0.28596923328260598</v>
       </c>
       <c r="V148" s="6">
         <v>0.032087700948785478</v>
@@ -21312,7 +21352,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21348,25 +21388,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>2779.5999999999999</v>
+      </c>
+      <c r="P158" s="5">
+        <v>2779.5999999999999</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.29280902078117688</v>
+      </c>
+      <c r="R158" s="7">
+        <v>27</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.27027027027027029</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.31556914663980429</v>
+      </c>
+      <c r="U158" s="6">
+        <v>-0.011812491005900131</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.039603540077709019</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0051331126780831777</v>
+      </c>
+      <c r="X158" s="8">
+        <v>31.511109523809523</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>6.4398821428571429</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>5.6880952380952383</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>12.561579</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>19.597619047619048</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-09-29).xlsx
@@ -911,25 +911,28 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-177</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+178</t>
   </si>
   <si>
     <t>26</t>
   </si>
   <si>
-    <t>R$ 921.506,09</t>
-  </si>
-  <si>
-    <t>R$ 4.901,63
-R$ 5.028,19</t>
+    <t>R$ 923.411,50</t>
+  </si>
+  <si>
+    <t>R$ 4.885,78
+R$ 5.010,65</t>
   </si>
   <si>
     <t>(13.8%)
-(11.5%)</t>
-  </si>
-  <si>
-    <t>51.6</t>
+(11.6%)</t>
+  </si>
+  <si>
+    <t>51.4</t>
   </si>
   <si>
     <t>(14.5%)</t>
@@ -941,7 +944,7 @@
     <t>(26.8%)</t>
   </si>
   <si>
-    <t>3.6%</t>
+    <t>3.7%</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -962,7 +965,7 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>11.8</t>
+    <t>11.9</t>
   </si>
   <si>
     <t>18.4</t>
@@ -5746,10 +5749,10 @@
         <v>-0.42307692307692313</v>
       </c>
       <c r="T34" s="6">
-        <v>5.3230304504494309E-05</v>
+        <v>0.0030060131576714428</v>
       </c>
       <c r="U34" s="6">
-        <v>-0.37859280042689841</v>
+        <v>-0.37564001757373139</v>
       </c>
       <c r="V34" s="6">
         <v>0.11858648368867343</v>
@@ -16092,7 +16095,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>27.831944</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19233,7 +19238,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19269,25 +19274,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>1905.4100000000001</v>
+      </c>
+      <c r="P141" s="5">
+        <v>1905.4100000000001</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>-0.39344810242632222</v>
+      </c>
+      <c r="R141" s="7">
+        <v>25</v>
+      </c>
+      <c r="S141" s="6">
+        <v>-0.26470588235294112</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.058113266960916551</v>
+      </c>
+      <c r="U141" s="6">
+        <v>-0.29829821403267537</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.19091691551949447</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.092670343915482747</v>
+      </c>
+      <c r="X141" s="8">
+        <v>20.619230769230771</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>4.9104166666666664</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>2.2111083333333332</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>6.2341870000000004</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>13.453846153846154</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>1</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -26177,7 +26218,9 @@
       <c r="AB195" s="8">
         <v>8.0656250000000007</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>15.098437000000001</v>
+      </c>
       <c r="AD195" s="8">
         <v>22.025521874999999</v>
       </c>
@@ -28497,112 +28540,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>